--- a/templates/office/EMP_DEG_130_배치프로그램설계서.xlsx
+++ b/templates/office/EMP_DEG_130_배치프로그램설계서.xlsx
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C12" s="92" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 SyncGuard AI 시스템 구축</t>
+          <t>한빛글로벌 SyncGuard AI 시스템 구축</t>
         </is>
       </c>
       <c r="D12" s="154" t="n"/>
@@ -2940,7 +2940,7 @@
     <row r="22" ht="22.5" customHeight="1" s="153">
       <c r="C22" s="157" t="inlineStr">
         <is>
-          <t>그로브소프트 (EMPASY)</t>
+          <t>엠파시 (EMPASY)</t>
         </is>
       </c>
       <c r="D22" s="158" t="n"/>

--- a/templates/office/EMP_DEG_130_배치프로그램설계서.xlsx
+++ b/templates/office/EMP_DEG_130_배치프로그램설계서.xlsx
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C12" s="92" t="inlineStr">
         <is>
-          <t>한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
       <c r="D12" s="154" t="n"/>
@@ -2946,7 +2946,7 @@
       <c r="D22" s="158" t="n"/>
       <c r="E22" s="159" t="inlineStr">
         <is>
-          <t>고객사명</t>
+          <t>주식회사 한빛글로벌</t>
         </is>
       </c>
       <c r="F22" s="160" t="n"/>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="D4" s="167" t="inlineStr">
         <is>
-          <t>SyncGuard AI 시스템 구축 기준 상세 작성</t>
+          <t>SyncFlow AI 시스템 구축 기준 상세 작성</t>
         </is>
       </c>
       <c r="E4" s="167" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="D5" s="74" t="inlineStr">
         <is>
-          <t>독립 Batch 서버(server-batch :18084) 분리 및 ProductLab 전성분·실증 동기화 배치를 매일 새벽 02:00 일 배치로 변경</t>
+          <t>독립 Batch 서버(server-batch :18084) 분리 및 PLM-Nexus 자재BOM·시험검증 동기화 배치를 매일 새벽 02:00 일 배치로 변경</t>
         </is>
       </c>
       <c r="E5" s="75" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C4" s="170" t="inlineStr">
         <is>
-          <t>식약처 법령·처분사례 수집 및 지능형 Diff 벡터화</t>
+          <t>공정위·표준원 법령·심결사례 수집 및 지능형 Diff 벡터화</t>
         </is>
       </c>
       <c r="D4" s="170" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="H4" s="170" t="inlineStr">
         <is>
-          <t>국가법령정보센터·식약처 행정처분 사례를 크롤링하고 기존 벡터 DB 조항과 지능형 비교(Diff)를 수행하여 신규·개정 조항만 선택적 재임베딩 및 버전 이력 적재</t>
+          <t>국가법령정보센터·공정위·표준원 불공정 심결 사례를 크롤링하고 기존 벡터 DB 조항과 지능형 비교(Diff)를 수행하여 신규·개정 조항만 선택적 재임베딩 및 버전 이력 적재</t>
         </is>
       </c>
       <c r="I4" s="170" t="inlineStr">
@@ -3385,7 +3385,7 @@
     <row r="5" ht="21" customHeight="1" s="153">
       <c r="A5" s="169" t="inlineStr">
         <is>
-          <t>실증연계</t>
+          <t>시험검증연계</t>
         </is>
       </c>
       <c r="B5" s="169" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="C5" s="170" t="inlineStr">
         <is>
-          <t>ProductLab 전성분·실증자료 동기화 ([Option] KT레몬)</t>
+          <t>PLM-Nexus 자재BOM·시험성적서 동기화 ([Option] HB-Monitor)</t>
         </is>
       </c>
       <c r="D5" s="170" t="inlineStr">
         <is>
-          <t>ProductLabSyncBatchJob</t>
+          <t>PlmNexusSyncBatchJob</t>
         </is>
       </c>
       <c r="E5" s="169" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="H5" s="170" t="inlineStr">
         <is>
-          <t>매일 새벽 02:00 정기 일 배치(cron: 0 0 2 * * ?)로 ProductLab 전성분·배합한도 마스터 및 신규 인체적용시험·효능 실증보고서를 동기화 (Batch 서버 :18084 전담)</t>
+          <t>매일 새벽 02:00 정기 일 배치(cron: 0 0 2 * * ?)로 PLM-Nexus 자재BOM·유해물질한도 마스터 및 신규 공인신뢰성시험·성능규격 시험검증보고서를 동기화 (Batch 서버 :18084 전담)</t>
         </is>
       </c>
       <c r="I5" s="170" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="I6" s="170" t="inlineStr">
         <is>
-          <t>정밀도 90% 미만 시 RA 리드에게 즉시 경보 발송</t>
+          <t>정밀도 90% 미만 시 QA 리드에게 즉시 경보 발송</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="C7" s="170" t="inlineStr">
         <is>
-          <t>임시 시안 파일 및 캐시 데이터 정제</t>
+          <t>임시 계약·도서 파일 및 캐시 데이터 정제</t>
         </is>
       </c>
       <c r="D7" s="170" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="H7" s="170" t="inlineStr">
         <is>
-          <t>임시 저장 후 30일 경과한 미완료 시안 임시 파일 및 만료된 Redis 캐시 항목 삭제</t>
+          <t>임시 저장 후 30일 경과한 미완료 계약·도서 임시 파일 및 만료된 Redis 캐시 항목 삭제</t>
         </is>
       </c>
       <c r="I7" s="170" t="inlineStr">
         <is>
-          <t>불변 감사로그 테이블(review_history_immutable)은 삭제 대상에서 영구 제외</t>
+          <t>불변 감사로그 테이블(verify_history_immutable)은 삭제 대상에서 영구 제외</t>
         </is>
       </c>
     </row>
@@ -3536,12 +3536,12 @@
       </c>
       <c r="C8" s="170" t="inlineStr">
         <is>
-          <t>MarketingHub 심의 결과 일괄 전송</t>
+          <t>SRM-Portal 검증 결과 일괄 전송</t>
         </is>
       </c>
       <c r="D8" s="170" t="inlineStr">
         <is>
-          <t>MarketingHubResultSyncJob</t>
+          <t>SrmPortalResultSyncJob</t>
         </is>
       </c>
       <c r="E8" s="169" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="H8" s="170" t="inlineStr">
         <is>
-          <t>RA 최종 확정된 심의 판정 결과서(PDF) 및 메타정보를 MarketingHub 광고심의 시스템으로 안전하게 회신</t>
+          <t>QA 최종 확정된 검증 판정 결과서(PDF) 및 메타정보를 SRM-Portal 계약·규격검증 시스템으로 안전하게 회신</t>
         </is>
       </c>
       <c r="I8" s="170" t="inlineStr">
@@ -3573,7 +3573,7 @@
     <row r="9" ht="20.25" customHeight="1" s="153">
       <c r="A9" s="36" t="inlineStr">
         <is>
-          <t>실증연계</t>
+          <t>시험검증연계</t>
         </is>
       </c>
       <c r="B9" s="37" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="C9" s="37" t="inlineStr">
         <is>
-          <t>[Option] KT 레몬 임상·실증 문서 일배치 동기화</t>
+          <t>[Option] HB-Monitor 신뢰성·시험검증 문서 일배치 동기화</t>
         </is>
       </c>
       <c r="D9" s="37" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="H9" s="41" t="inlineStr">
         <is>
-          <t>매일 새벽 02:30 정기 일 배치(cron: 0 30 2 * * ?)로 KT 레몬 임상·실증 문서 메타데이터 및 PG Vector(1536차원) 임베딩 동기화</t>
+          <t>매일 새벽 02:30 정기 일 배치(cron: 0 30 2 * * ?)로 HB-Monitor 신뢰성·시험검증 문서 메타데이터 및 PG Vector(1536차원) 임베딩 동기화</t>
         </is>
       </c>
       <c r="I9" s="42" t="inlineStr">
